--- a/docs/downloads/11/tbl_degats_personnes_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_personnes_alaotra_tous.xlsx
@@ -389,7 +389,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -413,7 +413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -437,7 +437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1037,7 +1037,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
